--- a/public/exports/64942212.xlsx
+++ b/public/exports/64942212.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -13939,12 +13939,12 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022757</t>
+          <t xml:space="preserve">200022759</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kelstrupgaard VVS &amp; Ingeniør forretning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087929</t>
+          <t xml:space="preserve">311087931</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087930</t>
+          <t xml:space="preserve">311087931</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -46564,12 +46564,12 @@
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606927</t>
+          <t xml:space="preserve">311606929</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M621" t="inlineStr">
@@ -46639,12 +46639,12 @@
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606927</t>
+          <t xml:space="preserve">311606929</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M622" t="inlineStr">
@@ -46789,12 +46789,12 @@
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606927</t>
+          <t xml:space="preserve">311606931</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M624" t="inlineStr">
@@ -46864,12 +46864,12 @@
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606925</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M625" t="inlineStr">
@@ -47164,12 +47164,12 @@
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606927</t>
+          <t xml:space="preserve">311606932</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M629" t="inlineStr">
@@ -47239,12 +47239,12 @@
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606927</t>
+          <t xml:space="preserve">311606932</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M630" t="inlineStr">
@@ -47314,12 +47314,12 @@
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606927</t>
+          <t xml:space="preserve">311606930</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M631" t="inlineStr">
@@ -56014,7 +56014,7 @@
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666811</t>
+          <t xml:space="preserve">311666822</t>
         </is>
       </c>
       <c r="L747" t="inlineStr">
@@ -57289,7 +57289,7 @@
       </c>
       <c r="K764" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671586</t>
+          <t xml:space="preserve">311671591</t>
         </is>
       </c>
       <c r="L764" t="inlineStr">
@@ -61789,7 +61789,7 @@
       </c>
       <c r="K824" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722451</t>
+          <t xml:space="preserve">311722479</t>
         </is>
       </c>
       <c r="L824" t="inlineStr">
@@ -61864,7 +61864,7 @@
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722451</t>
+          <t xml:space="preserve">311722479</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
@@ -62014,7 +62014,7 @@
       </c>
       <c r="K827" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722474</t>
+          <t xml:space="preserve">311722479</t>
         </is>
       </c>
       <c r="L827" t="inlineStr">
@@ -62389,7 +62389,7 @@
       </c>
       <c r="K832" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722439</t>
+          <t xml:space="preserve">311722479</t>
         </is>
       </c>
       <c r="L832" t="inlineStr">
@@ -62464,7 +62464,7 @@
       </c>
       <c r="K833" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722439</t>
+          <t xml:space="preserve">311722479</t>
         </is>
       </c>
       <c r="L833" t="inlineStr">
@@ -75814,12 +75814,12 @@
       </c>
       <c r="K1011" t="inlineStr">
         <is>
-          <t xml:space="preserve">311761210</t>
+          <t xml:space="preserve">311761230</t>
         </is>
       </c>
       <c r="L1011" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M1011" t="inlineStr">

--- a/public/exports/64942212.xlsx
+++ b/public/exports/64942212.xlsx
@@ -15814,7 +15814,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087931</t>
+          <t xml:space="preserve">311087929</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087931</t>
+          <t xml:space="preserve">311087933</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087931</t>
+          <t xml:space="preserve">311087932</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087931</t>
+          <t xml:space="preserve">311087930</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -31414,7 +31414,7 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t xml:space="preserve">311509832</t>
+          <t xml:space="preserve">311509833</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -38989,7 +38989,7 @@
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568903</t>
+          <t xml:space="preserve">311568904</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -46564,12 +46564,12 @@
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606929</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M621" t="inlineStr">
@@ -46639,12 +46639,12 @@
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606929</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M622" t="inlineStr">
@@ -46789,12 +46789,12 @@
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606931</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M624" t="inlineStr">
@@ -47164,12 +47164,12 @@
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606932</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M629" t="inlineStr">
@@ -47239,12 +47239,12 @@
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606932</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M630" t="inlineStr">
@@ -47314,12 +47314,12 @@
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t xml:space="preserve">311606930</t>
+          <t xml:space="preserve">311606927</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M631" t="inlineStr">
@@ -61714,7 +61714,7 @@
       </c>
       <c r="K823" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722481</t>
         </is>
       </c>
       <c r="L823" t="inlineStr">
@@ -61789,7 +61789,7 @@
       </c>
       <c r="K824" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722451</t>
         </is>
       </c>
       <c r="L824" t="inlineStr">
@@ -61864,7 +61864,7 @@
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722451</t>
         </is>
       </c>
       <c r="L825" t="inlineStr">
@@ -61939,7 +61939,7 @@
       </c>
       <c r="K826" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L826" t="inlineStr">
@@ -62014,7 +62014,7 @@
       </c>
       <c r="K827" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722474</t>
         </is>
       </c>
       <c r="L827" t="inlineStr">
@@ -62239,7 +62239,7 @@
       </c>
       <c r="K830" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L830" t="inlineStr">
@@ -62314,7 +62314,7 @@
       </c>
       <c r="K831" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L831" t="inlineStr">
@@ -62389,7 +62389,7 @@
       </c>
       <c r="K832" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722439</t>
         </is>
       </c>
       <c r="L832" t="inlineStr">
@@ -62464,7 +62464,7 @@
       </c>
       <c r="K833" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722439</t>
         </is>
       </c>
       <c r="L833" t="inlineStr">
@@ -62539,7 +62539,7 @@
       </c>
       <c r="K834" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L834" t="inlineStr">
@@ -62614,7 +62614,7 @@
       </c>
       <c r="K835" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L835" t="inlineStr">
@@ -62689,7 +62689,7 @@
       </c>
       <c r="K836" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L836" t="inlineStr">
@@ -62764,7 +62764,7 @@
       </c>
       <c r="K837" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L837" t="inlineStr">
@@ -62839,7 +62839,7 @@
       </c>
       <c r="K838" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L838" t="inlineStr">
@@ -62914,7 +62914,7 @@
       </c>
       <c r="K839" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L839" t="inlineStr">
@@ -62989,7 +62989,7 @@
       </c>
       <c r="K840" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722479</t>
+          <t xml:space="preserve">311722483</t>
         </is>
       </c>
       <c r="L840" t="inlineStr">
@@ -75941,30 +75941,30 @@
       </c>
       <c r="F1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blegdamsvej 132</t>
+          <t xml:space="preserve">Bernstorffsgade 17</t>
         </is>
       </c>
       <c r="G1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100</t>
+          <t xml:space="preserve">1577</t>
         </is>
       </c>
       <c r="H1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">6018285</t>
+          <t xml:space="preserve">6033506</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J1013">
-        <v>797</v>
+        <v>351</v>
       </c>
       <c r="K1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">311762263</t>
+          <t xml:space="preserve">311764545</t>
         </is>
       </c>
       <c r="L1013" t="inlineStr">
@@ -75974,7 +75974,7 @@
       </c>
       <c r="M1013" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-28</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="N1013" t="inlineStr">
@@ -76031,11 +76031,11 @@
       </c>
       <c r="I1014" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J1014">
-        <v>351</v>
+        <v>8189</v>
       </c>
       <c r="K1014" t="inlineStr">
         <is>
@@ -76091,30 +76091,30 @@
       </c>
       <c r="F1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernstorffsgade 17</t>
+          <t xml:space="preserve">Kirsebærhaven 20</t>
         </is>
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">1577</t>
+          <t xml:space="preserve">2500</t>
         </is>
       </c>
       <c r="H1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">6033506</t>
+          <t xml:space="preserve">6030058</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1015">
-        <v>8189</v>
+        <v>1197</v>
       </c>
       <c r="K1015" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764545</t>
+          <t xml:space="preserve">311764548</t>
         </is>
       </c>
       <c r="L1015" t="inlineStr">
@@ -76161,22 +76161,22 @@
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">217</t>
         </is>
       </c>
       <c r="F1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 20</t>
+          <t xml:space="preserve">Klostermosevej 117</t>
         </is>
       </c>
       <c r="G1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">2500</t>
+          <t xml:space="preserve">3000</t>
         </is>
       </c>
       <c r="H1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">6030058</t>
+          <t xml:space="preserve">5324053</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
@@ -76185,11 +76185,11 @@
         </is>
       </c>
       <c r="J1016">
-        <v>1197</v>
+        <v>740</v>
       </c>
       <c r="K1016" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764548</t>
+          <t xml:space="preserve">311764529</t>
         </is>
       </c>
       <c r="L1016" t="inlineStr">
@@ -76236,35 +76236,35 @@
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">217</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosevej 117</t>
+          <t xml:space="preserve">Staldgade 19</t>
         </is>
       </c>
       <c r="G1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000</t>
+          <t xml:space="preserve">1699</t>
         </is>
       </c>
       <c r="H1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">5324053</t>
+          <t xml:space="preserve">9622502</t>
         </is>
       </c>
       <c r="I1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="J1017">
-        <v>740</v>
+        <v>1534</v>
       </c>
       <c r="K1017" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764529</t>
+          <t xml:space="preserve">311764535</t>
         </is>
       </c>
       <c r="L1017" t="inlineStr">
@@ -76316,40 +76316,40 @@
       </c>
       <c r="F1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">Staldgade 19</t>
+          <t xml:space="preserve">Haderslevgade 6</t>
         </is>
       </c>
       <c r="G1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">1699</t>
+          <t xml:space="preserve">1671</t>
         </is>
       </c>
       <c r="H1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">9622502</t>
+          <t xml:space="preserve">6024580</t>
         </is>
       </c>
       <c r="I1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J1018">
-        <v>1534</v>
+        <v>617</v>
       </c>
       <c r="K1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764535</t>
+          <t xml:space="preserve">311768258</t>
         </is>
       </c>
       <c r="L1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M1018" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-06-21</t>
         </is>
       </c>
       <c r="N1018" t="inlineStr">
@@ -76391,30 +76391,30 @@
       </c>
       <c r="F1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haderslevgade 6</t>
+          <t xml:space="preserve">Kastrupvej 51</t>
         </is>
       </c>
       <c r="G1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671</t>
+          <t xml:space="preserve">2300</t>
         </is>
       </c>
       <c r="H1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">6024580</t>
+          <t xml:space="preserve">6013856</t>
         </is>
       </c>
       <c r="I1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1019">
-        <v>617</v>
+        <v>350</v>
       </c>
       <c r="K1019" t="inlineStr">
         <is>
-          <t xml:space="preserve">311768258</t>
+          <t xml:space="preserve">311768259</t>
         </is>
       </c>
       <c r="L1019" t="inlineStr">
@@ -76466,17 +76466,17 @@
       </c>
       <c r="F1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastrupvej 51</t>
+          <t xml:space="preserve">Ålekistevej 159</t>
         </is>
       </c>
       <c r="G1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">2300</t>
+          <t xml:space="preserve">2720</t>
         </is>
       </c>
       <c r="H1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013856</t>
+          <t xml:space="preserve">6030573</t>
         </is>
       </c>
       <c r="I1020" t="inlineStr">
@@ -76485,11 +76485,11 @@
         </is>
       </c>
       <c r="J1020">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="K1020" t="inlineStr">
         <is>
-          <t xml:space="preserve">311768259</t>
+          <t xml:space="preserve">311768260</t>
         </is>
       </c>
       <c r="L1020" t="inlineStr">
@@ -76541,40 +76541,40 @@
       </c>
       <c r="F1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålekistevej 159</t>
+          <t xml:space="preserve">Sjælør Boulevard 137</t>
         </is>
       </c>
       <c r="G1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720</t>
+          <t xml:space="preserve">2500</t>
         </is>
       </c>
       <c r="H1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">6030573</t>
+          <t xml:space="preserve">6027181</t>
         </is>
       </c>
       <c r="I1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J1021">
-        <v>404</v>
+        <v>1335</v>
       </c>
       <c r="K1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">311768260</t>
+          <t xml:space="preserve">311768828</t>
         </is>
       </c>
       <c r="L1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M1021" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-21</t>
+          <t xml:space="preserve">2034-06-24</t>
         </is>
       </c>
       <c r="N1021" t="inlineStr">
@@ -76616,35 +76616,35 @@
       </c>
       <c r="F1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sjælør Boulevard 137</t>
+          <t xml:space="preserve">Thomas Koppels Allé 13</t>
         </is>
       </c>
       <c r="G1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">2500</t>
+          <t xml:space="preserve">2450</t>
         </is>
       </c>
       <c r="H1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">6027181</t>
+          <t xml:space="preserve">9689527</t>
         </is>
       </c>
       <c r="I1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">742</t>
         </is>
       </c>
       <c r="J1022">
-        <v>1335</v>
+        <v>676</v>
       </c>
       <c r="K1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">311768828</t>
+          <t xml:space="preserve">311768748</t>
         </is>
       </c>
       <c r="L1022" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M1022" t="inlineStr">
@@ -76691,40 +76691,40 @@
       </c>
       <c r="F1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thomas Koppels Allé 13</t>
+          <t xml:space="preserve">Rådmandsgade 11</t>
         </is>
       </c>
       <c r="G1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">2450</t>
+          <t xml:space="preserve">2200</t>
         </is>
       </c>
       <c r="H1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">9689527</t>
+          <t xml:space="preserve">6018475</t>
         </is>
       </c>
       <c r="I1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">742</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1023">
-        <v>676</v>
+        <v>701</v>
       </c>
       <c r="K1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">311768748</t>
+          <t xml:space="preserve">311769456</t>
         </is>
       </c>
       <c r="L1023" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M1023" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-24</t>
+          <t xml:space="preserve">2034-06-26</t>
         </is>
       </c>
       <c r="N1023" t="inlineStr">
@@ -76761,22 +76761,22 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">190</t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådmandsgade 11</t>
+          <t xml:space="preserve">Bavnestedet 201</t>
         </is>
       </c>
       <c r="G1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">2200</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">6018475</t>
+          <t xml:space="preserve">2137307</t>
         </is>
       </c>
       <c r="I1024" t="inlineStr">
@@ -76785,11 +76785,11 @@
         </is>
       </c>
       <c r="J1024">
-        <v>701</v>
+        <v>864</v>
       </c>
       <c r="K1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">311769456</t>
+          <t xml:space="preserve">311771382</t>
         </is>
       </c>
       <c r="L1024" t="inlineStr">
@@ -76799,7 +76799,7 @@
       </c>
       <c r="M1024" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-26</t>
+          <t xml:space="preserve">2034-07-04</t>
         </is>
       </c>
       <c r="N1024" t="inlineStr">
@@ -76856,15 +76856,15 @@
       </c>
       <c r="I1025" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J1025">
-        <v>864</v>
+        <v>361</v>
       </c>
       <c r="K1025" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771382</t>
+          <t xml:space="preserve">311771383</t>
         </is>
       </c>
       <c r="L1025" t="inlineStr">
@@ -76926,12 +76926,12 @@
       </c>
       <c r="H1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137307</t>
+          <t xml:space="preserve">2137524</t>
         </is>
       </c>
       <c r="I1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J1026">
@@ -76939,7 +76939,7 @@
       </c>
       <c r="K1026" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771383</t>
+          <t xml:space="preserve">311771386</t>
         </is>
       </c>
       <c r="L1026" t="inlineStr">
@@ -76986,35 +76986,35 @@
       </c>
       <c r="E1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="F1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnestedet 201</t>
+          <t xml:space="preserve">Rosenvængets Allé 28</t>
         </is>
       </c>
       <c r="G1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">2100</t>
         </is>
       </c>
       <c r="H1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137524</t>
+          <t xml:space="preserve">6018243</t>
         </is>
       </c>
       <c r="I1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1027">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="K1027" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771386</t>
+          <t xml:space="preserve">311771394</t>
         </is>
       </c>
       <c r="L1027" t="inlineStr">
@@ -77066,7 +77066,7 @@
       </c>
       <c r="F1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvængets Allé 28</t>
+          <t xml:space="preserve">Ved Sporsløjfen 4</t>
         </is>
       </c>
       <c r="G1028" t="inlineStr">
@@ -77076,20 +77076,20 @@
       </c>
       <c r="H1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">6018243</t>
+          <t xml:space="preserve">9683864</t>
         </is>
       </c>
       <c r="I1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J1028">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="K1028" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771394</t>
+          <t xml:space="preserve">311771392</t>
         </is>
       </c>
       <c r="L1028" t="inlineStr">
@@ -77141,40 +77141,40 @@
       </c>
       <c r="F1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Sporsløjfen 4</t>
+          <t xml:space="preserve">Brønshøjvej 3</t>
         </is>
       </c>
       <c r="G1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100</t>
+          <t xml:space="preserve">2700</t>
         </is>
       </c>
       <c r="H1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">9683864</t>
+          <t xml:space="preserve">6001306</t>
         </is>
       </c>
       <c r="I1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J1029">
-        <v>379</v>
+        <v>1244</v>
       </c>
       <c r="K1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771392</t>
+          <t xml:space="preserve">311771717</t>
         </is>
       </c>
       <c r="L1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M1029" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-04</t>
+          <t xml:space="preserve">2034-07-05</t>
         </is>
       </c>
       <c r="N1029" t="inlineStr">
@@ -77211,40 +77211,40 @@
       </c>
       <c r="E1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">159</t>
         </is>
       </c>
       <c r="F1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brønshøjvej 3</t>
+          <t xml:space="preserve">Granvej 12</t>
         </is>
       </c>
       <c r="G1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">2700</t>
+          <t xml:space="preserve">2880</t>
         </is>
       </c>
       <c r="H1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">6001306</t>
+          <t xml:space="preserve">2085354</t>
         </is>
       </c>
       <c r="I1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J1030">
-        <v>1244</v>
+        <v>3456</v>
       </c>
       <c r="K1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771717</t>
+          <t xml:space="preserve">311771657</t>
         </is>
       </c>
       <c r="L1030" t="inlineStr">
         <is>
-          <t xml:space="preserve">LKH Rådgivning</t>
+          <t xml:space="preserve">pch-consult ApS</t>
         </is>
       </c>
       <c r="M1030" t="inlineStr">
@@ -77286,45 +77286,45 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">159</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">Granvej 12</t>
+          <t xml:space="preserve">Gunnar Nu Hansens Plads 1</t>
         </is>
       </c>
       <c r="G1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">2880</t>
+          <t xml:space="preserve">2100</t>
         </is>
       </c>
       <c r="H1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">2085354</t>
+          <t xml:space="preserve">6021932</t>
         </is>
       </c>
       <c r="I1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1031">
-        <v>3456</v>
+        <v>7344</v>
       </c>
       <c r="K1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771657</t>
+          <t xml:space="preserve">311772793</t>
         </is>
       </c>
       <c r="L1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">pch-consult ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M1031" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-05</t>
+          <t xml:space="preserve">2034-07-11</t>
         </is>
       </c>
       <c r="N1031" t="inlineStr">
@@ -77366,40 +77366,40 @@
       </c>
       <c r="F1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gunnar Nu Hansens Plads 1</t>
+          <t xml:space="preserve">Tietgensgade 67</t>
         </is>
       </c>
       <c r="G1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100</t>
+          <t xml:space="preserve">1704</t>
         </is>
       </c>
       <c r="H1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">6021932</t>
+          <t xml:space="preserve">8119353</t>
         </is>
       </c>
       <c r="I1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="J1032">
-        <v>7344</v>
+        <v>270</v>
       </c>
       <c r="K1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772793</t>
+          <t xml:space="preserve">311774780</t>
         </is>
       </c>
       <c r="L1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Conergi</t>
         </is>
       </c>
       <c r="M1032" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-11</t>
+          <t xml:space="preserve">2034-07-23</t>
         </is>
       </c>
       <c r="N1032" t="inlineStr">
@@ -77441,40 +77441,40 @@
       </c>
       <c r="F1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tietgensgade 67</t>
+          <t xml:space="preserve">Gammel Kalkbrænderi Vej 2</t>
         </is>
       </c>
       <c r="G1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">1704</t>
+          <t xml:space="preserve">2100</t>
         </is>
       </c>
       <c r="H1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">8119353</t>
+          <t xml:space="preserve">8971534</t>
         </is>
       </c>
       <c r="I1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J1033">
-        <v>270</v>
+        <v>1946</v>
       </c>
       <c r="K1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">311774780</t>
+          <t xml:space="preserve">311781921</t>
         </is>
       </c>
       <c r="L1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conergi</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M1033" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-23</t>
+          <t xml:space="preserve">2034-09-02</t>
         </is>
       </c>
       <c r="N1033" t="inlineStr">
@@ -77516,7 +77516,7 @@
       </c>
       <c r="F1034" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Kalkbrænderi Vej 2</t>
+          <t xml:space="preserve">Randersgade 12</t>
         </is>
       </c>
       <c r="G1034" t="inlineStr">
@@ -77531,11 +77531,11 @@
       </c>
       <c r="I1034" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J1034">
-        <v>1946</v>
+        <v>1230</v>
       </c>
       <c r="K1034" t="inlineStr">
         <is>
@@ -77591,40 +77591,40 @@
       </c>
       <c r="F1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">Randersgade 12</t>
+          <t xml:space="preserve">Saxtorphsvej 11</t>
         </is>
       </c>
       <c r="G1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100</t>
+          <t xml:space="preserve">2500</t>
         </is>
       </c>
       <c r="H1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">8971534</t>
+          <t xml:space="preserve">9556845</t>
         </is>
       </c>
       <c r="I1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J1035">
-        <v>1230</v>
+        <v>1740</v>
       </c>
       <c r="K1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">311781921</t>
+          <t xml:space="preserve">311782130</t>
         </is>
       </c>
       <c r="L1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M1035" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-02</t>
+          <t xml:space="preserve">2034-09-03</t>
         </is>
       </c>
       <c r="N1035" t="inlineStr">
@@ -77666,7 +77666,7 @@
       </c>
       <c r="F1036" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saxtorphsvej 11</t>
+          <t xml:space="preserve">Saxtorphsvej 31</t>
         </is>
       </c>
       <c r="G1036" t="inlineStr">
@@ -77681,11 +77681,11 @@
       </c>
       <c r="I1036" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J1036">
-        <v>1740</v>
+        <v>728</v>
       </c>
       <c r="K1036" t="inlineStr">
         <is>
@@ -77741,40 +77741,40 @@
       </c>
       <c r="F1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">Saxtorphsvej 31</t>
+          <t xml:space="preserve">Skelbækgade 19</t>
         </is>
       </c>
       <c r="G1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">2500</t>
+          <t xml:space="preserve">1717</t>
         </is>
       </c>
       <c r="H1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">9556845</t>
+          <t xml:space="preserve">6024150</t>
         </is>
       </c>
       <c r="I1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="J1037">
-        <v>728</v>
+        <v>10652</v>
       </c>
       <c r="K1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">311782130</t>
+          <t xml:space="preserve">311784633</t>
         </is>
       </c>
       <c r="L1037" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OS Engineering ApS</t>
         </is>
       </c>
       <c r="M1037" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-03</t>
+          <t xml:space="preserve">2034-09-13</t>
         </is>
       </c>
       <c r="N1037" t="inlineStr">
@@ -77816,40 +77816,40 @@
       </c>
       <c r="F1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skelbækgade 19</t>
+          <t xml:space="preserve">Hans Kirks Vej 8</t>
         </is>
       </c>
       <c r="G1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">1717</t>
+          <t xml:space="preserve">2200</t>
         </is>
       </c>
       <c r="H1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">6024150</t>
+          <t xml:space="preserve">8339484</t>
         </is>
       </c>
       <c r="I1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve">116</t>
         </is>
       </c>
       <c r="J1038">
-        <v>10652</v>
+        <v>2606</v>
       </c>
       <c r="K1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">311784633</t>
+          <t xml:space="preserve">311786220</t>
         </is>
       </c>
       <c r="L1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">OS Engineering ApS</t>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
         </is>
       </c>
       <c r="M1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-13</t>
+          <t xml:space="preserve">2034-09-20</t>
         </is>
       </c>
       <c r="N1038" t="inlineStr">
@@ -77891,40 +77891,40 @@
       </c>
       <c r="F1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hans Kirks Vej 8</t>
+          <t xml:space="preserve">Frederiksborgvej 125</t>
         </is>
       </c>
       <c r="G1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">2200</t>
+          <t xml:space="preserve">2400</t>
         </is>
       </c>
       <c r="H1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">8339484</t>
+          <t xml:space="preserve">6022484</t>
         </is>
       </c>
       <c r="I1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">116</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1039">
-        <v>2606</v>
+        <v>397</v>
       </c>
       <c r="K1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">311786220</t>
+          <t xml:space="preserve">311790023</t>
         </is>
       </c>
       <c r="L1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M1039" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-20</t>
+          <t xml:space="preserve">2034-10-07</t>
         </is>
       </c>
       <c r="N1039" t="inlineStr">
@@ -77981,11 +77981,11 @@
       </c>
       <c r="I1040" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J1040">
-        <v>397</v>
+        <v>259</v>
       </c>
       <c r="K1040" t="inlineStr">
         <is>
@@ -78041,7 +78041,7 @@
       </c>
       <c r="F1041" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksborgvej 125</t>
+          <t xml:space="preserve">Rådvadsvej 64</t>
         </is>
       </c>
       <c r="G1041" t="inlineStr">
@@ -78051,20 +78051,20 @@
       </c>
       <c r="H1041" t="inlineStr">
         <is>
-          <t xml:space="preserve">6022484</t>
+          <t xml:space="preserve">9686208</t>
         </is>
       </c>
       <c r="I1041" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J1041">
-        <v>259</v>
+        <v>515</v>
       </c>
       <c r="K1041" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790023</t>
+          <t xml:space="preserve">311790018</t>
         </is>
       </c>
       <c r="L1041" t="inlineStr">
@@ -78131,15 +78131,15 @@
       </c>
       <c r="I1042" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J1042">
-        <v>515</v>
+        <v>858</v>
       </c>
       <c r="K1042" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790018</t>
+          <t xml:space="preserve">311790016</t>
         </is>
       </c>
       <c r="L1042" t="inlineStr">
@@ -78186,45 +78186,45 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">101</t>
+          <t xml:space="preserve">259</t>
         </is>
       </c>
       <c r="F1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådvadsvej 64</t>
+          <t xml:space="preserve">Spanagervej 14A</t>
         </is>
       </c>
       <c r="G1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400</t>
+          <t xml:space="preserve">4623</t>
         </is>
       </c>
       <c r="H1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">9686208</t>
+          <t xml:space="preserve">8940886</t>
         </is>
       </c>
       <c r="I1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J1043">
-        <v>858</v>
+        <v>1048</v>
       </c>
       <c r="K1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790016</t>
+          <t xml:space="preserve">311796116</t>
         </is>
       </c>
       <c r="L1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M1043" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-07</t>
+          <t xml:space="preserve">2034-11-07</t>
         </is>
       </c>
       <c r="N1043" t="inlineStr">
@@ -78266,7 +78266,7 @@
       </c>
       <c r="F1044" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spanagervej 14A</t>
+          <t xml:space="preserve">Spanagervej 14E</t>
         </is>
       </c>
       <c r="G1044" t="inlineStr">
@@ -78281,11 +78281,11 @@
       </c>
       <c r="I1044" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J1044">
-        <v>1048</v>
+        <v>345</v>
       </c>
       <c r="K1044" t="inlineStr">
         <is>
@@ -78341,7 +78341,7 @@
       </c>
       <c r="F1045" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spanagervej 14E</t>
+          <t xml:space="preserve">Spanagervej 14F</t>
         </is>
       </c>
       <c r="G1045" t="inlineStr">
@@ -78356,7 +78356,7 @@
       </c>
       <c r="I1045" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J1045">
@@ -78411,45 +78411,45 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">259</t>
+          <t xml:space="preserve">101</t>
         </is>
       </c>
       <c r="F1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spanagervej 14F</t>
+          <t xml:space="preserve">Sundevedsgade 8</t>
         </is>
       </c>
       <c r="G1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">4623</t>
+          <t xml:space="preserve">1751</t>
         </is>
       </c>
       <c r="H1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940886</t>
+          <t xml:space="preserve">6023837</t>
         </is>
       </c>
       <c r="I1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1046">
-        <v>345</v>
+        <v>1019</v>
       </c>
       <c r="K1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">311796116</t>
+          <t xml:space="preserve">311797347</t>
         </is>
       </c>
       <c r="L1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">pch-consult ApS</t>
         </is>
       </c>
       <c r="M1046" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-07</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="N1046" t="inlineStr">
@@ -78491,40 +78491,40 @@
       </c>
       <c r="F1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundevedsgade 8</t>
+          <t xml:space="preserve">Holmbladsgade 33</t>
         </is>
       </c>
       <c r="G1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">1751</t>
+          <t xml:space="preserve">2300</t>
         </is>
       </c>
       <c r="H1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">6023837</t>
+          <t xml:space="preserve">134032</t>
         </is>
       </c>
       <c r="I1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J1047">
-        <v>1019</v>
+        <v>475</v>
       </c>
       <c r="K1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797347</t>
+          <t xml:space="preserve">311806796</t>
         </is>
       </c>
       <c r="L1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">pch-consult ApS</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M1047" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2035-01-20</t>
         </is>
       </c>
       <c r="N1047" t="inlineStr">
@@ -78566,7 +78566,7 @@
       </c>
       <c r="F1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmbladsgade 33</t>
+          <t xml:space="preserve">Parmagade 2A</t>
         </is>
       </c>
       <c r="G1048" t="inlineStr">
@@ -78576,30 +78576,30 @@
       </c>
       <c r="H1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">134032</t>
+          <t xml:space="preserve">418987, 418988, 418989, 418990, 418991, 418992, 418993, 418994, 418995, 418996, 418997, 418998, 418999, 419000</t>
         </is>
       </c>
       <c r="I1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1048">
-        <v>475</v>
+        <v>4943</v>
       </c>
       <c r="K1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">311806796</t>
+          <t xml:space="preserve">311820700</t>
         </is>
       </c>
       <c r="L1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M1048" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-20</t>
+          <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
       <c r="N1048" t="inlineStr">
@@ -78641,17 +78641,17 @@
       </c>
       <c r="F1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parmagade 2A</t>
+          <t xml:space="preserve">Nørre Allé 7</t>
         </is>
       </c>
       <c r="G1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">2300</t>
+          <t xml:space="preserve">2200</t>
         </is>
       </c>
       <c r="H1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">418987, 418988, 418989, 418990, 418991, 418992, 418993, 418994, 418995, 418996, 418997, 418998, 418999, 419000</t>
+          <t xml:space="preserve">6018049</t>
         </is>
       </c>
       <c r="I1049" t="inlineStr">
@@ -78660,21 +78660,21 @@
         </is>
       </c>
       <c r="J1049">
-        <v>4943</v>
+        <v>1581</v>
       </c>
       <c r="K1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820700</t>
+          <t xml:space="preserve">311823147</t>
         </is>
       </c>
       <c r="L1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M1049" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-27</t>
+          <t xml:space="preserve">2035-04-07</t>
         </is>
       </c>
       <c r="N1049" t="inlineStr">
@@ -78731,11 +78731,11 @@
       </c>
       <c r="I1050" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J1050">
-        <v>1581</v>
+        <v>345</v>
       </c>
       <c r="K1050" t="inlineStr">
         <is>
@@ -78791,30 +78791,30 @@
       </c>
       <c r="F1051" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Allé 7</t>
+          <t xml:space="preserve">Øresundsvej 4</t>
         </is>
       </c>
       <c r="G1051" t="inlineStr">
         <is>
-          <t xml:space="preserve">2200</t>
+          <t xml:space="preserve">2300</t>
         </is>
       </c>
       <c r="H1051" t="inlineStr">
         <is>
-          <t xml:space="preserve">6018049</t>
+          <t xml:space="preserve">10272766</t>
         </is>
       </c>
       <c r="I1051" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J1051">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="K1051" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823147</t>
+          <t xml:space="preserve">311832600</t>
         </is>
       </c>
       <c r="L1051" t="inlineStr">
@@ -78824,7 +78824,7 @@
       </c>
       <c r="M1051" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-07</t>
+          <t xml:space="preserve">2035-05-19</t>
         </is>
       </c>
       <c r="N1051" t="inlineStr">
@@ -78866,7 +78866,7 @@
       </c>
       <c r="F1052" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øresundsvej 4</t>
+          <t xml:space="preserve">Øresundsvej 6B</t>
         </is>
       </c>
       <c r="G1052" t="inlineStr">
@@ -78881,15 +78881,15 @@
       </c>
       <c r="I1052" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J1052">
-        <v>363</v>
+        <v>1731</v>
       </c>
       <c r="K1052" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832600</t>
+          <t xml:space="preserve">311832602</t>
         </is>
       </c>
       <c r="L1052" t="inlineStr">
@@ -78941,40 +78941,40 @@
       </c>
       <c r="F1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øresundsvej 6B</t>
+          <t xml:space="preserve">Enghavevej 90B</t>
         </is>
       </c>
       <c r="G1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">2300</t>
+          <t xml:space="preserve">2450</t>
         </is>
       </c>
       <c r="H1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">10272766</t>
+          <t xml:space="preserve">6025118</t>
         </is>
       </c>
       <c r="I1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J1053">
-        <v>1731</v>
+        <v>655</v>
       </c>
       <c r="K1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832602</t>
+          <t xml:space="preserve">311852217</t>
         </is>
       </c>
       <c r="L1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M1053" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-19</t>
+          <t xml:space="preserve">2035-08-28</t>
         </is>
       </c>
       <c r="N1053" t="inlineStr">
@@ -79016,40 +79016,40 @@
       </c>
       <c r="F1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 90B</t>
+          <t xml:space="preserve">Sionsgade 1</t>
         </is>
       </c>
       <c r="G1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">2450</t>
+          <t xml:space="preserve">2100</t>
         </is>
       </c>
       <c r="H1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">6025118</t>
+          <t xml:space="preserve">9842148</t>
         </is>
       </c>
       <c r="I1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1054">
-        <v>655</v>
+        <v>3000</v>
       </c>
       <c r="K1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">311852217</t>
+          <t xml:space="preserve">311859292</t>
         </is>
       </c>
       <c r="L1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M1054" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-28</t>
+          <t xml:space="preserve">2035-10-01</t>
         </is>
       </c>
       <c r="N1054" t="inlineStr">
@@ -79106,11 +79106,11 @@
       </c>
       <c r="I1055" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J1055">
-        <v>3000</v>
+        <v>1190</v>
       </c>
       <c r="K1055" t="inlineStr">
         <is>
@@ -79181,11 +79181,11 @@
       </c>
       <c r="I1056" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J1056">
-        <v>1190</v>
+        <v>260</v>
       </c>
       <c r="K1056" t="inlineStr">
         <is>
@@ -79241,7 +79241,7 @@
       </c>
       <c r="F1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sionsgade 1</t>
+          <t xml:space="preserve">Biskop Krags Vænge 3</t>
         </is>
       </c>
       <c r="G1057" t="inlineStr">
@@ -79251,30 +79251,30 @@
       </c>
       <c r="H1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">9842148</t>
+          <t xml:space="preserve">8118354</t>
         </is>
       </c>
       <c r="I1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J1057">
-        <v>260</v>
+        <v>730</v>
       </c>
       <c r="K1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">311859292</t>
+          <t xml:space="preserve">311860444</t>
         </is>
       </c>
       <c r="L1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">OS Engineering ApS</t>
         </is>
       </c>
       <c r="M1057" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-01</t>
+          <t xml:space="preserve">2035-10-07</t>
         </is>
       </c>
       <c r="N1057" t="inlineStr">
@@ -79331,15 +79331,15 @@
       </c>
       <c r="I1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1058">
-        <v>730</v>
+        <v>3404</v>
       </c>
       <c r="K1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860444</t>
+          <t xml:space="preserve">311860574</t>
         </is>
       </c>
       <c r="L1058" t="inlineStr">
@@ -79349,7 +79349,7 @@
       </c>
       <c r="M1058" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-07</t>
+          <t xml:space="preserve">2035-10-08</t>
         </is>
       </c>
       <c r="N1058" t="inlineStr">
@@ -79406,15 +79406,15 @@
       </c>
       <c r="I1059" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J1059">
-        <v>3404</v>
+        <v>1437</v>
       </c>
       <c r="K1059" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860574</t>
+          <t xml:space="preserve">311860789</t>
         </is>
       </c>
       <c r="L1059" t="inlineStr">
@@ -79481,15 +79481,15 @@
       </c>
       <c r="I1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J1060">
-        <v>1437</v>
+        <v>1372</v>
       </c>
       <c r="K1060" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860789</t>
+          <t xml:space="preserve">311860783</t>
         </is>
       </c>
       <c r="L1060" t="inlineStr">
@@ -79541,40 +79541,40 @@
       </c>
       <c r="F1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biskop Krags Vænge 3</t>
+          <t xml:space="preserve">Ørholmgade 8</t>
         </is>
       </c>
       <c r="G1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100</t>
+          <t xml:space="preserve">2200</t>
         </is>
       </c>
       <c r="H1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">8118354</t>
+          <t xml:space="preserve">6021095</t>
         </is>
       </c>
       <c r="I1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1061">
-        <v>1372</v>
+        <v>4579</v>
       </c>
       <c r="K1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">311860783</t>
+          <t xml:space="preserve">311865962</t>
         </is>
       </c>
       <c r="L1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">OS Engineering ApS</t>
+          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
         </is>
       </c>
       <c r="M1061" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-08</t>
+          <t xml:space="preserve">2035-10-30</t>
         </is>
       </c>
       <c r="N1061" t="inlineStr">
@@ -79616,40 +79616,40 @@
       </c>
       <c r="F1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørholmgade 8</t>
+          <t xml:space="preserve">Amsterdamvej 38</t>
         </is>
       </c>
       <c r="G1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">2200</t>
+          <t xml:space="preserve">2300</t>
         </is>
       </c>
       <c r="H1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">6021095</t>
+          <t xml:space="preserve">501519, 501520, 501521, 501522, 501523, 501524, 8193008</t>
         </is>
       </c>
       <c r="I1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J1062">
-        <v>4579</v>
+        <v>438</v>
       </c>
       <c r="K1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865962</t>
+          <t xml:space="preserve">311878521</t>
         </is>
       </c>
       <c r="L1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plan 1 Byggerådgivning A/S</t>
+          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
         </is>
       </c>
       <c r="M1062" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-30</t>
+          <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
       <c r="N1062" t="inlineStr">
@@ -79691,40 +79691,40 @@
       </c>
       <c r="F1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amsterdamvej 38</t>
+          <t xml:space="preserve">Møntmestervej 54</t>
         </is>
       </c>
       <c r="G1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">2300</t>
+          <t xml:space="preserve">2400</t>
         </is>
       </c>
       <c r="H1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">501519, 501520, 501521, 501522, 501523, 501524, 8193008</t>
+          <t xml:space="preserve">6023562</t>
         </is>
       </c>
       <c r="I1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1063">
-        <v>438</v>
+        <v>924</v>
       </c>
       <c r="K1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878521</t>
+          <t xml:space="preserve">311889888</t>
         </is>
       </c>
       <c r="L1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bang &amp; Beenfeldt A/S</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M1063" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-26</t>
+          <t xml:space="preserve">2036-03-25</t>
         </is>
       </c>
       <c r="N1063" t="inlineStr">
@@ -79766,40 +79766,40 @@
       </c>
       <c r="F1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møntmestervej 54</t>
+          <t xml:space="preserve">Enghavevej 88</t>
         </is>
       </c>
       <c r="G1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400</t>
+          <t xml:space="preserve">2450</t>
         </is>
       </c>
       <c r="H1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">6023562</t>
+          <t xml:space="preserve">6025118</t>
         </is>
       </c>
       <c r="I1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J1064">
-        <v>924</v>
+        <v>1112</v>
       </c>
       <c r="K1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">311889888</t>
+          <t xml:space="preserve">311898803</t>
         </is>
       </c>
       <c r="L1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">Inspec ApS</t>
         </is>
       </c>
       <c r="M1064" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-25</t>
+          <t xml:space="preserve">2036-05-04</t>
         </is>
       </c>
       <c r="N1064" t="inlineStr">
@@ -79841,40 +79841,40 @@
       </c>
       <c r="F1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 88</t>
+          <t xml:space="preserve">Hanstholmvej 10</t>
         </is>
       </c>
       <c r="G1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">2450</t>
+          <t xml:space="preserve">2720</t>
         </is>
       </c>
       <c r="H1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">6025118</t>
+          <t xml:space="preserve">6030580</t>
         </is>
       </c>
       <c r="I1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="J1065">
-        <v>1112</v>
+        <v>474</v>
       </c>
       <c r="K1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">311898803</t>
+          <t xml:space="preserve">311923936</t>
         </is>
       </c>
       <c r="L1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspec ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M1065" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-04</t>
+          <t xml:space="preserve">2036-09-04</t>
         </is>
       </c>
       <c r="N1065" t="inlineStr">
@@ -79916,7 +79916,7 @@
       </c>
       <c r="F1066" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanstholmvej 10</t>
+          <t xml:space="preserve">Hirtshalsvej 6A</t>
         </is>
       </c>
       <c r="G1066" t="inlineStr">
@@ -79931,11 +79931,11 @@
       </c>
       <c r="I1066" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J1066">
-        <v>474</v>
+        <v>1966</v>
       </c>
       <c r="K1066" t="inlineStr">
         <is>
@@ -79991,7 +79991,7 @@
       </c>
       <c r="F1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hirtshalsvej 6A</t>
+          <t xml:space="preserve">Hirtshalsvej 6B</t>
         </is>
       </c>
       <c r="G1067" t="inlineStr">
@@ -80006,11 +80006,11 @@
       </c>
       <c r="I1067" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J1067">
-        <v>1966</v>
+        <v>1200</v>
       </c>
       <c r="K1067" t="inlineStr">
         <is>
@@ -80066,7 +80066,7 @@
       </c>
       <c r="F1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hirtshalsvej 6B</t>
+          <t xml:space="preserve">Hirtshalsvej 6C</t>
         </is>
       </c>
       <c r="G1068" t="inlineStr">
@@ -80081,11 +80081,11 @@
       </c>
       <c r="I1068" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="J1068">
-        <v>1200</v>
+        <v>2331</v>
       </c>
       <c r="K1068" t="inlineStr">
         <is>
@@ -80141,7 +80141,7 @@
       </c>
       <c r="F1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hirtshalsvej 6C</t>
+          <t xml:space="preserve">Klitmøllervej 1</t>
         </is>
       </c>
       <c r="G1069" t="inlineStr">
@@ -80156,11 +80156,11 @@
       </c>
       <c r="I1069" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J1069">
-        <v>2331</v>
+        <v>720</v>
       </c>
       <c r="K1069" t="inlineStr">
         <is>
@@ -80231,11 +80231,11 @@
       </c>
       <c r="I1070" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J1070">
-        <v>720</v>
+        <v>400</v>
       </c>
       <c r="K1070" t="inlineStr">
         <is>
@@ -80291,7 +80291,7 @@
       </c>
       <c r="F1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klitmøllervej 1</t>
+          <t xml:space="preserve">Klitmøllervej 7B</t>
         </is>
       </c>
       <c r="G1071" t="inlineStr">
@@ -80306,11 +80306,11 @@
       </c>
       <c r="I1071" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="J1071">
-        <v>400</v>
+        <v>487</v>
       </c>
       <c r="K1071" t="inlineStr">
         <is>
@@ -80366,7 +80366,7 @@
       </c>
       <c r="F1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klitmøllervej 7B</t>
+          <t xml:space="preserve">Ålekistevej 121</t>
         </is>
       </c>
       <c r="G1072" t="inlineStr">
@@ -80381,11 +80381,11 @@
       </c>
       <c r="I1072" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J1072">
-        <v>487</v>
+        <v>819</v>
       </c>
       <c r="K1072" t="inlineStr">
         <is>
@@ -80456,11 +80456,11 @@
       </c>
       <c r="I1073" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J1073">
-        <v>819</v>
+        <v>5031</v>
       </c>
       <c r="K1073" t="inlineStr">
         <is>
@@ -80516,17 +80516,17 @@
       </c>
       <c r="F1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålekistevej 121</t>
+          <t xml:space="preserve">Blegdamsvej 132</t>
         </is>
       </c>
       <c r="G1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720</t>
+          <t xml:space="preserve">2100</t>
         </is>
       </c>
       <c r="H1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">6030580</t>
+          <t xml:space="preserve">6018285</t>
         </is>
       </c>
       <c r="I1074" t="inlineStr">
@@ -80535,21 +80535,21 @@
         </is>
       </c>
       <c r="J1074">
-        <v>5031</v>
+        <v>797</v>
       </c>
       <c r="K1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923936</t>
+          <t xml:space="preserve">311927224</t>
         </is>
       </c>
       <c r="L1074" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EKJ Rådgivende Ingeniør A/S</t>
         </is>
       </c>
       <c r="M1074" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-04</t>
+          <t xml:space="preserve">2036-09-22</t>
         </is>
       </c>
       <c r="N1074" t="inlineStr">
